--- a/demo/data/остатки-склад-Москва-2026-06-29.xlsx
+++ b/demo/data/остатки-склад-Москва-2026-06-29.xlsx
@@ -487,7 +487,7 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>87</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -504,7 +504,7 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -521,7 +521,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -538,7 +538,7 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -555,7 +555,7 @@
         <v>35</v>
       </c>
       <c r="E6">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -572,7 +572,7 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -589,7 +589,7 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -606,7 +606,7 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>56</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -623,7 +623,7 @@
         <v>35</v>
       </c>
       <c r="E10">
-        <v>56</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -640,7 +640,7 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -657,7 +657,7 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -674,7 +674,7 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:5">
